--- a/Materials_TAPM_assetsV1.xlsx
+++ b/Materials_TAPM_assetsV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70f25f7605021e1a/ESG_Future/Tennis Aus/Phase III/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="8_{9AE8AC5B-770D-4243-BAF3-9CB5FEADCB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE8665BA-B43F-4D9C-A89B-453B17681D0B}"/>
+  <xr:revisionPtr revIDLastSave="566" documentId="8_{9AE8AC5B-770D-4243-BAF3-9CB5FEADCB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBA67B7F-9A29-45FB-9F32-8BA878F90F7D}"/>
   <bookViews>
-    <workbookView xWindow="9790" yWindow="-18230" windowWidth="25650" windowHeight="14170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12320" yWindow="-19470" windowWidth="25650" windowHeight="16810" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AO Materials Mgt" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="300">
   <si>
     <t>PLAN_ID:</t>
   </si>
@@ -848,9 +848,6 @@
     <t>As required</t>
   </si>
   <si>
-    <t>To track materials and assets TA PMs can use the browser based Materials Management Plan or smartsheets/ xls tracking assets which can be uploaded</t>
-  </si>
-  <si>
     <t>New Serial number</t>
   </si>
   <si>
@@ -966,13 +963,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Refurb &amp; Replacement </t>
+    <t>AO27 Materials Management Plan (anyone managing TA owned assets)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormant asset - not used greater than 1 year </t>
+    <t>Refurb /replacement for next AO</t>
   </si>
   <si>
-    <t>AO27 Materials Management Plan (anyone managing TA owned assets)</t>
+    <t>To track materials and assets TA PMs/ builders can use the browser based Materials Management Plan or smartsheets/ xls tracking assets which can be uploaded</t>
   </si>
 </sst>
 </file>
@@ -1569,9 +1566,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1580,6 +1574,9 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2676,18 +2673,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
       <c r="L1" s="58" t="s">
         <v>226</v>
       </c>
@@ -2726,11 +2723,11 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="71" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="8"/>
@@ -2816,11 +2813,11 @@
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="8"/>
@@ -2833,10 +2830,10 @@
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="72" t="s">
         <v>237</v>
       </c>
-      <c r="C11" s="73"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="1"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -2848,10 +2845,10 @@
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="72" t="s">
         <v>238</v>
       </c>
-      <c r="C12" s="73"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2863,10 +2860,10 @@
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="72" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="73"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2930,7 +2927,7 @@
         <v>243</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>244</v>
@@ -2951,10 +2948,10 @@
         <v>249</v>
       </c>
       <c r="J16" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="K16" s="13" t="s">
         <v>295</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>296</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>250</v>
@@ -13800,7 +13797,7 @@
       <c r="I508" s="15"/>
       <c r="J508" s="16"/>
       <c r="K508" s="16"/>
-      <c r="L508" s="16"/>
+      <c r="L508" s="14"/>
       <c r="M508" s="16"/>
       <c r="N508" s="53"/>
       <c r="O508" s="14"/>
@@ -13822,7 +13819,7 @@
       <c r="I509" s="15"/>
       <c r="J509" s="16"/>
       <c r="K509" s="16"/>
-      <c r="L509" s="16"/>
+      <c r="L509" s="14"/>
       <c r="M509" s="16"/>
       <c r="N509" s="53"/>
       <c r="O509" s="14"/>
@@ -13844,7 +13841,7 @@
       <c r="I510" s="15"/>
       <c r="J510" s="16"/>
       <c r="K510" s="16"/>
-      <c r="L510" s="16"/>
+      <c r="L510" s="14"/>
       <c r="M510" s="16"/>
       <c r="N510" s="53"/>
       <c r="O510" s="14"/>
@@ -13866,7 +13863,7 @@
       <c r="I511" s="15"/>
       <c r="J511" s="16"/>
       <c r="K511" s="16"/>
-      <c r="L511" s="16"/>
+      <c r="L511" s="14"/>
       <c r="M511" s="16"/>
       <c r="N511" s="53"/>
       <c r="O511" s="14"/>
@@ -13888,7 +13885,7 @@
       <c r="I512" s="15"/>
       <c r="J512" s="16"/>
       <c r="K512" s="16"/>
-      <c r="L512" s="16"/>
+      <c r="L512" s="14"/>
       <c r="M512" s="16"/>
       <c r="N512" s="53"/>
       <c r="O512" s="14"/>
@@ -13910,7 +13907,7 @@
       <c r="I513" s="15"/>
       <c r="J513" s="16"/>
       <c r="K513" s="16"/>
-      <c r="L513" s="16"/>
+      <c r="L513" s="14"/>
       <c r="M513" s="16"/>
       <c r="N513" s="53"/>
       <c r="O513" s="14"/>
@@ -13932,7 +13929,7 @@
       <c r="I514" s="15"/>
       <c r="J514" s="16"/>
       <c r="K514" s="16"/>
-      <c r="L514" s="16"/>
+      <c r="L514" s="14"/>
       <c r="M514" s="16"/>
       <c r="N514" s="53"/>
       <c r="O514" s="14"/>
@@ -13954,7 +13951,7 @@
       <c r="I515" s="15"/>
       <c r="J515" s="16"/>
       <c r="K515" s="16"/>
-      <c r="L515" s="16"/>
+      <c r="L515" s="14"/>
       <c r="M515" s="16"/>
       <c r="N515" s="53"/>
       <c r="O515" s="14"/>
@@ -13976,7 +13973,7 @@
       <c r="I516" s="15"/>
       <c r="J516" s="16"/>
       <c r="K516" s="16"/>
-      <c r="L516" s="16"/>
+      <c r="L516" s="14"/>
       <c r="M516" s="16"/>
       <c r="N516" s="53"/>
       <c r="O516" s="14"/>
@@ -13998,7 +13995,7 @@
       <c r="I517" s="15"/>
       <c r="J517" s="16"/>
       <c r="K517" s="16"/>
-      <c r="L517" s="16"/>
+      <c r="L517" s="14"/>
       <c r="M517" s="16"/>
       <c r="N517" s="53"/>
       <c r="O517" s="14"/>
@@ -14020,7 +14017,7 @@
       <c r="I518" s="15"/>
       <c r="J518" s="16"/>
       <c r="K518" s="16"/>
-      <c r="L518" s="16"/>
+      <c r="L518" s="14"/>
       <c r="M518" s="16"/>
       <c r="N518" s="53"/>
       <c r="O518" s="14"/>
@@ -14042,7 +14039,7 @@
       <c r="I519" s="15"/>
       <c r="J519" s="16"/>
       <c r="K519" s="16"/>
-      <c r="L519" s="16"/>
+      <c r="L519" s="14"/>
       <c r="M519" s="16"/>
       <c r="N519" s="53"/>
       <c r="O519" s="14"/>
@@ -14064,7 +14061,7 @@
       <c r="I520" s="15"/>
       <c r="J520" s="16"/>
       <c r="K520" s="16"/>
-      <c r="L520" s="16"/>
+      <c r="L520" s="14"/>
       <c r="M520" s="16"/>
       <c r="N520" s="53"/>
       <c r="O520" s="14"/>
@@ -14086,7 +14083,7 @@
       <c r="I521" s="15"/>
       <c r="J521" s="16"/>
       <c r="K521" s="16"/>
-      <c r="L521" s="16"/>
+      <c r="L521" s="14"/>
       <c r="M521" s="16"/>
       <c r="N521" s="53"/>
       <c r="O521" s="14"/>
@@ -14108,7 +14105,7 @@
       <c r="I522" s="15"/>
       <c r="J522" s="16"/>
       <c r="K522" s="16"/>
-      <c r="L522" s="16"/>
+      <c r="L522" s="14"/>
       <c r="M522" s="16"/>
       <c r="N522" s="53"/>
       <c r="O522" s="14"/>
@@ -14130,7 +14127,7 @@
       <c r="I523" s="15"/>
       <c r="J523" s="16"/>
       <c r="K523" s="16"/>
-      <c r="L523" s="16"/>
+      <c r="L523" s="14"/>
       <c r="M523" s="16"/>
       <c r="N523" s="53"/>
       <c r="O523" s="14"/>
@@ -14152,7 +14149,7 @@
       <c r="I524" s="15"/>
       <c r="J524" s="16"/>
       <c r="K524" s="16"/>
-      <c r="L524" s="16"/>
+      <c r="L524" s="14"/>
       <c r="M524" s="16"/>
       <c r="N524" s="53"/>
       <c r="O524" s="14"/>
@@ -14174,7 +14171,7 @@
       <c r="I525" s="15"/>
       <c r="J525" s="16"/>
       <c r="K525" s="16"/>
-      <c r="L525" s="16"/>
+      <c r="L525" s="14"/>
       <c r="M525" s="16"/>
       <c r="N525" s="53"/>
       <c r="O525" s="14"/>
@@ -14196,7 +14193,7 @@
       <c r="I526" s="15"/>
       <c r="J526" s="16"/>
       <c r="K526" s="16"/>
-      <c r="L526" s="16"/>
+      <c r="L526" s="14"/>
       <c r="M526" s="16"/>
       <c r="N526" s="53"/>
       <c r="O526" s="14"/>
@@ -14218,7 +14215,7 @@
       <c r="I527" s="15"/>
       <c r="J527" s="16"/>
       <c r="K527" s="16"/>
-      <c r="L527" s="16"/>
+      <c r="L527" s="14"/>
       <c r="M527" s="16"/>
       <c r="N527" s="53"/>
       <c r="O527" s="14"/>
@@ -14240,7 +14237,7 @@
       <c r="I528" s="15"/>
       <c r="J528" s="16"/>
       <c r="K528" s="16"/>
-      <c r="L528" s="16"/>
+      <c r="L528" s="14"/>
       <c r="M528" s="16"/>
       <c r="N528" s="53"/>
       <c r="O528" s="14"/>
@@ -14262,7 +14259,7 @@
       <c r="I529" s="15"/>
       <c r="J529" s="16"/>
       <c r="K529" s="16"/>
-      <c r="L529" s="16"/>
+      <c r="L529" s="14"/>
       <c r="M529" s="16"/>
       <c r="N529" s="53"/>
       <c r="O529" s="14"/>
@@ -14284,7 +14281,7 @@
       <c r="I530" s="15"/>
       <c r="J530" s="16"/>
       <c r="K530" s="16"/>
-      <c r="L530" s="16"/>
+      <c r="L530" s="14"/>
       <c r="M530" s="16"/>
       <c r="N530" s="53"/>
       <c r="O530" s="14"/>
@@ -14306,7 +14303,7 @@
       <c r="I531" s="15"/>
       <c r="J531" s="16"/>
       <c r="K531" s="16"/>
-      <c r="L531" s="16"/>
+      <c r="L531" s="14"/>
       <c r="M531" s="16"/>
       <c r="N531" s="53"/>
       <c r="O531" s="14"/>
@@ -14328,7 +14325,7 @@
       <c r="I532" s="15"/>
       <c r="J532" s="16"/>
       <c r="K532" s="16"/>
-      <c r="L532" s="16"/>
+      <c r="L532" s="14"/>
       <c r="M532" s="16"/>
       <c r="N532" s="53"/>
       <c r="O532" s="14"/>
@@ -14350,7 +14347,7 @@
       <c r="I533" s="15"/>
       <c r="J533" s="16"/>
       <c r="K533" s="16"/>
-      <c r="L533" s="16"/>
+      <c r="L533" s="14"/>
       <c r="M533" s="16"/>
       <c r="N533" s="53"/>
       <c r="O533" s="14"/>
@@ -14372,7 +14369,7 @@
       <c r="I534" s="15"/>
       <c r="J534" s="16"/>
       <c r="K534" s="16"/>
-      <c r="L534" s="16"/>
+      <c r="L534" s="14"/>
       <c r="M534" s="16"/>
       <c r="N534" s="53"/>
       <c r="O534" s="14"/>
@@ -14394,7 +14391,7 @@
       <c r="I535" s="15"/>
       <c r="J535" s="16"/>
       <c r="K535" s="16"/>
-      <c r="L535" s="16"/>
+      <c r="L535" s="14"/>
       <c r="M535" s="16"/>
       <c r="N535" s="53"/>
       <c r="O535" s="14"/>
@@ -14416,7 +14413,7 @@
       <c r="I536" s="15"/>
       <c r="J536" s="16"/>
       <c r="K536" s="16"/>
-      <c r="L536" s="16"/>
+      <c r="L536" s="14"/>
       <c r="M536" s="16"/>
       <c r="N536" s="53"/>
       <c r="O536" s="14"/>
@@ -14438,7 +14435,7 @@
       <c r="I537" s="15"/>
       <c r="J537" s="16"/>
       <c r="K537" s="16"/>
-      <c r="L537" s="16"/>
+      <c r="L537" s="14"/>
       <c r="M537" s="16"/>
       <c r="N537" s="53"/>
       <c r="O537" s="14"/>
@@ -14460,7 +14457,7 @@
       <c r="I538" s="15"/>
       <c r="J538" s="16"/>
       <c r="K538" s="16"/>
-      <c r="L538" s="16"/>
+      <c r="L538" s="14"/>
       <c r="M538" s="16"/>
       <c r="N538" s="53"/>
       <c r="O538" s="14"/>
@@ -14482,7 +14479,7 @@
       <c r="I539" s="15"/>
       <c r="J539" s="16"/>
       <c r="K539" s="16"/>
-      <c r="L539" s="16"/>
+      <c r="L539" s="14"/>
       <c r="M539" s="16"/>
       <c r="N539" s="53"/>
       <c r="O539" s="14"/>
@@ -14504,7 +14501,7 @@
       <c r="I540" s="15"/>
       <c r="J540" s="16"/>
       <c r="K540" s="16"/>
-      <c r="L540" s="16"/>
+      <c r="L540" s="14"/>
       <c r="M540" s="16"/>
       <c r="N540" s="53"/>
       <c r="O540" s="14"/>
@@ -14526,7 +14523,7 @@
       <c r="I541" s="15"/>
       <c r="J541" s="16"/>
       <c r="K541" s="16"/>
-      <c r="L541" s="16"/>
+      <c r="L541" s="14"/>
       <c r="M541" s="16"/>
       <c r="N541" s="53"/>
       <c r="O541" s="14"/>
@@ -14548,7 +14545,7 @@
       <c r="I542" s="15"/>
       <c r="J542" s="16"/>
       <c r="K542" s="16"/>
-      <c r="L542" s="16"/>
+      <c r="L542" s="14"/>
       <c r="M542" s="16"/>
       <c r="N542" s="53"/>
       <c r="O542" s="14"/>
@@ -14570,7 +14567,7 @@
       <c r="I543" s="15"/>
       <c r="J543" s="16"/>
       <c r="K543" s="16"/>
-      <c r="L543" s="16"/>
+      <c r="L543" s="14"/>
       <c r="M543" s="16"/>
       <c r="N543" s="53"/>
       <c r="O543" s="14"/>
@@ -14592,7 +14589,7 @@
       <c r="I544" s="15"/>
       <c r="J544" s="16"/>
       <c r="K544" s="16"/>
-      <c r="L544" s="16"/>
+      <c r="L544" s="14"/>
       <c r="M544" s="16"/>
       <c r="N544" s="53"/>
       <c r="O544" s="14"/>
@@ -14614,7 +14611,7 @@
       <c r="I545" s="15"/>
       <c r="J545" s="16"/>
       <c r="K545" s="16"/>
-      <c r="L545" s="16"/>
+      <c r="L545" s="14"/>
       <c r="M545" s="16"/>
       <c r="N545" s="53"/>
       <c r="O545" s="14"/>
@@ -14636,7 +14633,7 @@
       <c r="I546" s="15"/>
       <c r="J546" s="16"/>
       <c r="K546" s="16"/>
-      <c r="L546" s="16"/>
+      <c r="L546" s="14"/>
       <c r="M546" s="16"/>
       <c r="N546" s="53"/>
       <c r="O546" s="14"/>
@@ -14658,7 +14655,7 @@
       <c r="I547" s="15"/>
       <c r="J547" s="16"/>
       <c r="K547" s="16"/>
-      <c r="L547" s="16"/>
+      <c r="L547" s="14"/>
       <c r="M547" s="16"/>
       <c r="N547" s="53"/>
       <c r="O547" s="14"/>
@@ -14680,7 +14677,7 @@
       <c r="I548" s="15"/>
       <c r="J548" s="16"/>
       <c r="K548" s="16"/>
-      <c r="L548" s="16"/>
+      <c r="L548" s="14"/>
       <c r="M548" s="16"/>
       <c r="N548" s="53"/>
       <c r="O548" s="14"/>
@@ -14702,7 +14699,7 @@
       <c r="I549" s="15"/>
       <c r="J549" s="16"/>
       <c r="K549" s="16"/>
-      <c r="L549" s="16"/>
+      <c r="L549" s="14"/>
       <c r="M549" s="16"/>
       <c r="N549" s="53"/>
       <c r="O549" s="14"/>
@@ -14724,7 +14721,7 @@
       <c r="I550" s="15"/>
       <c r="J550" s="16"/>
       <c r="K550" s="16"/>
-      <c r="L550" s="16"/>
+      <c r="L550" s="14"/>
       <c r="M550" s="16"/>
       <c r="N550" s="53"/>
       <c r="O550" s="14"/>
@@ -14746,7 +14743,7 @@
       <c r="I551" s="15"/>
       <c r="J551" s="16"/>
       <c r="K551" s="16"/>
-      <c r="L551" s="16"/>
+      <c r="L551" s="14"/>
       <c r="M551" s="16"/>
       <c r="N551" s="53"/>
       <c r="O551" s="14"/>
@@ -14768,7 +14765,7 @@
       <c r="I552" s="15"/>
       <c r="J552" s="16"/>
       <c r="K552" s="16"/>
-      <c r="L552" s="16"/>
+      <c r="L552" s="14"/>
       <c r="M552" s="16"/>
       <c r="N552" s="53"/>
       <c r="O552" s="14"/>
@@ -14790,7 +14787,7 @@
       <c r="I553" s="15"/>
       <c r="J553" s="16"/>
       <c r="K553" s="16"/>
-      <c r="L553" s="16"/>
+      <c r="L553" s="14"/>
       <c r="M553" s="16"/>
       <c r="N553" s="53"/>
       <c r="O553" s="14"/>
@@ -14812,7 +14809,7 @@
       <c r="I554" s="15"/>
       <c r="J554" s="16"/>
       <c r="K554" s="16"/>
-      <c r="L554" s="16"/>
+      <c r="L554" s="14"/>
       <c r="M554" s="16"/>
       <c r="N554" s="53"/>
       <c r="O554" s="14"/>
@@ -14834,7 +14831,7 @@
       <c r="I555" s="15"/>
       <c r="J555" s="16"/>
       <c r="K555" s="16"/>
-      <c r="L555" s="16"/>
+      <c r="L555" s="14"/>
       <c r="M555" s="16"/>
       <c r="N555" s="53"/>
       <c r="O555" s="14"/>
@@ -14856,7 +14853,7 @@
       <c r="I556" s="15"/>
       <c r="J556" s="16"/>
       <c r="K556" s="16"/>
-      <c r="L556" s="16"/>
+      <c r="L556" s="14"/>
       <c r="M556" s="16"/>
       <c r="N556" s="53"/>
       <c r="O556" s="14"/>
@@ -14878,7 +14875,7 @@
       <c r="I557" s="15"/>
       <c r="J557" s="16"/>
       <c r="K557" s="16"/>
-      <c r="L557" s="16"/>
+      <c r="L557" s="14"/>
       <c r="M557" s="16"/>
       <c r="N557" s="53"/>
       <c r="O557" s="14"/>
@@ -14900,7 +14897,7 @@
       <c r="I558" s="15"/>
       <c r="J558" s="16"/>
       <c r="K558" s="16"/>
-      <c r="L558" s="16"/>
+      <c r="L558" s="14"/>
       <c r="M558" s="16"/>
       <c r="N558" s="53"/>
       <c r="O558" s="14"/>
@@ -14922,7 +14919,7 @@
       <c r="I559" s="15"/>
       <c r="J559" s="16"/>
       <c r="K559" s="16"/>
-      <c r="L559" s="16"/>
+      <c r="L559" s="14"/>
       <c r="M559" s="16"/>
       <c r="N559" s="53"/>
       <c r="O559" s="14"/>
@@ -14944,7 +14941,7 @@
       <c r="I560" s="15"/>
       <c r="J560" s="16"/>
       <c r="K560" s="16"/>
-      <c r="L560" s="16"/>
+      <c r="L560" s="14"/>
       <c r="M560" s="16"/>
       <c r="N560" s="53"/>
       <c r="O560" s="14"/>
@@ -14966,7 +14963,7 @@
       <c r="I561" s="15"/>
       <c r="J561" s="16"/>
       <c r="K561" s="16"/>
-      <c r="L561" s="16"/>
+      <c r="L561" s="14"/>
       <c r="M561" s="16"/>
       <c r="N561" s="53"/>
       <c r="O561" s="14"/>
@@ -14988,7 +14985,7 @@
       <c r="I562" s="15"/>
       <c r="J562" s="16"/>
       <c r="K562" s="16"/>
-      <c r="L562" s="16"/>
+      <c r="L562" s="14"/>
       <c r="M562" s="16"/>
       <c r="N562" s="53"/>
       <c r="O562" s="14"/>
@@ -15010,7 +15007,7 @@
       <c r="I563" s="15"/>
       <c r="J563" s="16"/>
       <c r="K563" s="16"/>
-      <c r="L563" s="16"/>
+      <c r="L563" s="14"/>
       <c r="M563" s="16"/>
       <c r="N563" s="53"/>
       <c r="O563" s="14"/>
@@ -15032,7 +15029,7 @@
       <c r="I564" s="15"/>
       <c r="J564" s="16"/>
       <c r="K564" s="16"/>
-      <c r="L564" s="16"/>
+      <c r="L564" s="14"/>
       <c r="M564" s="16"/>
       <c r="N564" s="53"/>
       <c r="O564" s="14"/>
@@ -15054,7 +15051,7 @@
       <c r="I565" s="15"/>
       <c r="J565" s="16"/>
       <c r="K565" s="16"/>
-      <c r="L565" s="16"/>
+      <c r="L565" s="14"/>
       <c r="M565" s="16"/>
       <c r="N565" s="53"/>
       <c r="O565" s="14"/>
@@ -15076,7 +15073,7 @@
       <c r="I566" s="15"/>
       <c r="J566" s="16"/>
       <c r="K566" s="16"/>
-      <c r="L566" s="16"/>
+      <c r="L566" s="14"/>
       <c r="M566" s="16"/>
       <c r="N566" s="53"/>
       <c r="O566" s="14"/>
@@ -15098,7 +15095,7 @@
       <c r="I567" s="15"/>
       <c r="J567" s="16"/>
       <c r="K567" s="16"/>
-      <c r="L567" s="16"/>
+      <c r="L567" s="14"/>
       <c r="M567" s="16"/>
       <c r="N567" s="53"/>
       <c r="O567" s="14"/>
@@ -15120,7 +15117,7 @@
       <c r="I568" s="15"/>
       <c r="J568" s="16"/>
       <c r="K568" s="16"/>
-      <c r="L568" s="16"/>
+      <c r="L568" s="14"/>
       <c r="M568" s="16"/>
       <c r="N568" s="53"/>
       <c r="O568" s="14"/>
@@ -15142,7 +15139,7 @@
       <c r="I569" s="15"/>
       <c r="J569" s="16"/>
       <c r="K569" s="16"/>
-      <c r="L569" s="16"/>
+      <c r="L569" s="14"/>
       <c r="M569" s="16"/>
       <c r="N569" s="53"/>
       <c r="O569" s="14"/>
@@ -15164,7 +15161,7 @@
       <c r="I570" s="15"/>
       <c r="J570" s="16"/>
       <c r="K570" s="16"/>
-      <c r="L570" s="16"/>
+      <c r="L570" s="14"/>
       <c r="M570" s="16"/>
       <c r="N570" s="53"/>
       <c r="O570" s="14"/>
@@ -15186,7 +15183,7 @@
       <c r="I571" s="15"/>
       <c r="J571" s="16"/>
       <c r="K571" s="16"/>
-      <c r="L571" s="16"/>
+      <c r="L571" s="14"/>
       <c r="M571" s="16"/>
       <c r="N571" s="53"/>
       <c r="O571" s="14"/>
@@ -15208,7 +15205,7 @@
       <c r="I572" s="15"/>
       <c r="J572" s="16"/>
       <c r="K572" s="16"/>
-      <c r="L572" s="16"/>
+      <c r="L572" s="14"/>
       <c r="M572" s="16"/>
       <c r="N572" s="53"/>
       <c r="O572" s="14"/>
@@ -15230,7 +15227,7 @@
       <c r="I573" s="15"/>
       <c r="J573" s="16"/>
       <c r="K573" s="16"/>
-      <c r="L573" s="16"/>
+      <c r="L573" s="14"/>
       <c r="M573" s="16"/>
       <c r="N573" s="53"/>
       <c r="O573" s="14"/>
@@ -15252,7 +15249,7 @@
       <c r="I574" s="15"/>
       <c r="J574" s="16"/>
       <c r="K574" s="16"/>
-      <c r="L574" s="16"/>
+      <c r="L574" s="14"/>
       <c r="M574" s="16"/>
       <c r="N574" s="53"/>
       <c r="O574" s="14"/>
@@ -15274,7 +15271,7 @@
       <c r="I575" s="15"/>
       <c r="J575" s="16"/>
       <c r="K575" s="16"/>
-      <c r="L575" s="16"/>
+      <c r="L575" s="14"/>
       <c r="M575" s="16"/>
       <c r="N575" s="53"/>
       <c r="O575" s="14"/>
@@ -15296,7 +15293,7 @@
       <c r="I576" s="15"/>
       <c r="J576" s="16"/>
       <c r="K576" s="16"/>
-      <c r="L576" s="16"/>
+      <c r="L576" s="14"/>
       <c r="M576" s="16"/>
       <c r="N576" s="53"/>
       <c r="O576" s="14"/>
@@ -15318,7 +15315,7 @@
       <c r="I577" s="15"/>
       <c r="J577" s="16"/>
       <c r="K577" s="16"/>
-      <c r="L577" s="16"/>
+      <c r="L577" s="14"/>
       <c r="M577" s="16"/>
       <c r="N577" s="53"/>
       <c r="O577" s="14"/>
@@ -15340,7 +15337,7 @@
       <c r="I578" s="15"/>
       <c r="J578" s="16"/>
       <c r="K578" s="16"/>
-      <c r="L578" s="16"/>
+      <c r="L578" s="14"/>
       <c r="M578" s="16"/>
       <c r="N578" s="53"/>
       <c r="O578" s="14"/>
@@ -15362,7 +15359,7 @@
       <c r="I579" s="15"/>
       <c r="J579" s="16"/>
       <c r="K579" s="16"/>
-      <c r="L579" s="16"/>
+      <c r="L579" s="14"/>
       <c r="M579" s="16"/>
       <c r="N579" s="53"/>
       <c r="O579" s="14"/>
@@ -15384,7 +15381,7 @@
       <c r="I580" s="15"/>
       <c r="J580" s="16"/>
       <c r="K580" s="16"/>
-      <c r="L580" s="16"/>
+      <c r="L580" s="14"/>
       <c r="M580" s="16"/>
       <c r="N580" s="53"/>
       <c r="O580" s="14"/>
@@ -15406,7 +15403,7 @@
       <c r="I581" s="15"/>
       <c r="J581" s="16"/>
       <c r="K581" s="16"/>
-      <c r="L581" s="16"/>
+      <c r="L581" s="14"/>
       <c r="M581" s="16"/>
       <c r="N581" s="53"/>
       <c r="O581" s="14"/>
@@ -15428,7 +15425,7 @@
       <c r="I582" s="15"/>
       <c r="J582" s="16"/>
       <c r="K582" s="16"/>
-      <c r="L582" s="16"/>
+      <c r="L582" s="14"/>
       <c r="M582" s="16"/>
       <c r="N582" s="53"/>
       <c r="O582" s="14"/>
@@ -15450,7 +15447,7 @@
       <c r="I583" s="15"/>
       <c r="J583" s="16"/>
       <c r="K583" s="16"/>
-      <c r="L583" s="16"/>
+      <c r="L583" s="14"/>
       <c r="M583" s="16"/>
       <c r="N583" s="53"/>
       <c r="O583" s="14"/>
@@ -15472,7 +15469,7 @@
       <c r="I584" s="15"/>
       <c r="J584" s="16"/>
       <c r="K584" s="16"/>
-      <c r="L584" s="16"/>
+      <c r="L584" s="14"/>
       <c r="M584" s="16"/>
       <c r="N584" s="53"/>
       <c r="O584" s="14"/>
@@ -15494,7 +15491,7 @@
       <c r="I585" s="15"/>
       <c r="J585" s="16"/>
       <c r="K585" s="16"/>
-      <c r="L585" s="16"/>
+      <c r="L585" s="14"/>
       <c r="M585" s="16"/>
       <c r="N585" s="53"/>
       <c r="O585" s="14"/>
@@ -15516,7 +15513,7 @@
       <c r="I586" s="15"/>
       <c r="J586" s="16"/>
       <c r="K586" s="16"/>
-      <c r="L586" s="16"/>
+      <c r="L586" s="14"/>
       <c r="M586" s="16"/>
       <c r="N586" s="53"/>
       <c r="O586" s="14"/>
@@ -15538,7 +15535,7 @@
       <c r="I587" s="15"/>
       <c r="J587" s="16"/>
       <c r="K587" s="16"/>
-      <c r="L587" s="16"/>
+      <c r="L587" s="14"/>
       <c r="M587" s="16"/>
       <c r="N587" s="53"/>
       <c r="O587" s="14"/>
@@ -15560,7 +15557,7 @@
       <c r="I588" s="15"/>
       <c r="J588" s="16"/>
       <c r="K588" s="16"/>
-      <c r="L588" s="16"/>
+      <c r="L588" s="14"/>
       <c r="M588" s="16"/>
       <c r="N588" s="53"/>
       <c r="O588" s="14"/>
@@ -15582,7 +15579,7 @@
       <c r="I589" s="15"/>
       <c r="J589" s="16"/>
       <c r="K589" s="16"/>
-      <c r="L589" s="16"/>
+      <c r="L589" s="14"/>
       <c r="M589" s="16"/>
       <c r="N589" s="53"/>
       <c r="O589" s="14"/>
@@ -15604,7 +15601,7 @@
       <c r="I590" s="15"/>
       <c r="J590" s="16"/>
       <c r="K590" s="16"/>
-      <c r="L590" s="16"/>
+      <c r="L590" s="14"/>
       <c r="M590" s="16"/>
       <c r="N590" s="53"/>
       <c r="O590" s="14"/>
@@ -15626,7 +15623,7 @@
       <c r="I591" s="15"/>
       <c r="J591" s="16"/>
       <c r="K591" s="16"/>
-      <c r="L591" s="16"/>
+      <c r="L591" s="14"/>
       <c r="M591" s="16"/>
       <c r="N591" s="53"/>
       <c r="O591" s="14"/>
@@ -15648,7 +15645,7 @@
       <c r="I592" s="15"/>
       <c r="J592" s="16"/>
       <c r="K592" s="16"/>
-      <c r="L592" s="16"/>
+      <c r="L592" s="14"/>
       <c r="M592" s="16"/>
       <c r="N592" s="53"/>
       <c r="O592" s="14"/>
@@ -15670,7 +15667,7 @@
       <c r="I593" s="15"/>
       <c r="J593" s="16"/>
       <c r="K593" s="16"/>
-      <c r="L593" s="16"/>
+      <c r="L593" s="14"/>
       <c r="M593" s="16"/>
       <c r="N593" s="53"/>
       <c r="O593" s="14"/>
@@ -15692,7 +15689,7 @@
       <c r="I594" s="15"/>
       <c r="J594" s="16"/>
       <c r="K594" s="16"/>
-      <c r="L594" s="16"/>
+      <c r="L594" s="14"/>
       <c r="M594" s="16"/>
       <c r="N594" s="53"/>
       <c r="O594" s="14"/>
@@ -15714,7 +15711,7 @@
       <c r="I595" s="15"/>
       <c r="J595" s="16"/>
       <c r="K595" s="16"/>
-      <c r="L595" s="16"/>
+      <c r="L595" s="14"/>
       <c r="M595" s="16"/>
       <c r="N595" s="53"/>
       <c r="O595" s="14"/>
@@ -15736,7 +15733,7 @@
       <c r="I596" s="15"/>
       <c r="J596" s="16"/>
       <c r="K596" s="16"/>
-      <c r="L596" s="16"/>
+      <c r="L596" s="14"/>
       <c r="M596" s="16"/>
       <c r="N596" s="53"/>
       <c r="O596" s="14"/>
@@ -15758,7 +15755,7 @@
       <c r="I597" s="15"/>
       <c r="J597" s="16"/>
       <c r="K597" s="16"/>
-      <c r="L597" s="16"/>
+      <c r="L597" s="14"/>
       <c r="M597" s="16"/>
       <c r="N597" s="53"/>
       <c r="O597" s="14"/>
@@ -15780,7 +15777,7 @@
       <c r="I598" s="15"/>
       <c r="J598" s="16"/>
       <c r="K598" s="16"/>
-      <c r="L598" s="16"/>
+      <c r="L598" s="14"/>
       <c r="M598" s="16"/>
       <c r="N598" s="53"/>
       <c r="O598" s="14"/>
@@ -15802,7 +15799,7 @@
       <c r="I599" s="15"/>
       <c r="J599" s="16"/>
       <c r="K599" s="16"/>
-      <c r="L599" s="16"/>
+      <c r="L599" s="14"/>
       <c r="M599" s="16"/>
       <c r="N599" s="53"/>
       <c r="O599" s="14"/>
@@ -15824,7 +15821,7 @@
       <c r="I600" s="15"/>
       <c r="J600" s="16"/>
       <c r="K600" s="16"/>
-      <c r="L600" s="16"/>
+      <c r="L600" s="14"/>
       <c r="M600" s="16"/>
       <c r="N600" s="53"/>
       <c r="O600" s="14"/>
@@ -15846,7 +15843,7 @@
       <c r="I601" s="15"/>
       <c r="J601" s="16"/>
       <c r="K601" s="16"/>
-      <c r="L601" s="16"/>
+      <c r="L601" s="14"/>
       <c r="M601" s="16"/>
       <c r="N601" s="53"/>
       <c r="O601" s="14"/>
@@ -15868,7 +15865,7 @@
       <c r="I602" s="15"/>
       <c r="J602" s="16"/>
       <c r="K602" s="16"/>
-      <c r="L602" s="16"/>
+      <c r="L602" s="14"/>
       <c r="M602" s="16"/>
       <c r="N602" s="53"/>
       <c r="O602" s="14"/>
@@ -15890,7 +15887,7 @@
       <c r="I603" s="15"/>
       <c r="J603" s="16"/>
       <c r="K603" s="16"/>
-      <c r="L603" s="16"/>
+      <c r="L603" s="14"/>
       <c r="M603" s="16"/>
       <c r="N603" s="53"/>
       <c r="O603" s="14"/>
@@ -15912,7 +15909,7 @@
       <c r="I604" s="15"/>
       <c r="J604" s="16"/>
       <c r="K604" s="16"/>
-      <c r="L604" s="16"/>
+      <c r="L604" s="14"/>
       <c r="M604" s="16"/>
       <c r="N604" s="53"/>
       <c r="O604" s="14"/>
@@ -15940,15 +15937,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{93DF118A-2674-44C8-AD6D-0CEF649FF15F}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F038BD03-0598-4F37-BA42-DDD4046F775E}">
           <x14:formula1>
             <xm:f>Sheet1!$A$3:$A$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>L17:L508</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F038BD03-0598-4F37-BA42-DDD4046F775E}">
-          <x14:formula1>
-            <xm:f>Sheet1!$A$3:$A$11</xm:f>
           </x14:formula1>
           <xm:sqref>N17:N604</xm:sqref>
         </x14:dataValidation>
@@ -15969,6 +15960,12 @@
             <xm:f>Sheet1!$A$49:$A$75</xm:f>
           </x14:formula1>
           <xm:sqref>I17:I604</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7E09714A-E8FD-4491-AD5A-4163732EC08C}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$3:$A$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>L17:L604</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16018,7 +16015,7 @@
     <row r="2" spans="1:23" s="49" customFormat="1" ht="13" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:23" s="49" customFormat="1" ht="13" x14ac:dyDescent="0.35">
       <c r="A3" s="49" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="13" x14ac:dyDescent="0.35">
@@ -16089,12 +16086,12 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="73" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="70"/>
+      <c r="A19" s="73"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="65"/>
@@ -47322,7 +47319,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>212</v>
@@ -47330,33 +47327,25 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>170</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>172</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="22" t="s">
         <v>215</v>
       </c>
     </row>
@@ -47441,7 +47430,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>195</v>
@@ -47465,7 +47454,7 @@
         <v>207</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -47488,7 +47477,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>200</v>
@@ -47497,7 +47486,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>201</v>
@@ -47509,7 +47498,7 @@
         <v>173</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C34" s="17"/>
     </row>
@@ -47550,13 +47539,13 @@
         <v>184</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C39" s="17"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>202</v>
@@ -47613,122 +47602,122 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="69" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="69" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="69" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="69" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="69" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="69" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="69" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="69" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="69" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="69" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="69" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="69" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="69" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
